--- a/output/details/2026-05-29/preprocessed_data.xlsx
+++ b/output/details/2026-05-29/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46171</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1167881995408512</v>
+        <v>-0.1228273678079064</v>
       </c>
       <c r="C2" t="n">
-        <v>0.13757134057166</v>
+        <v>-0.1426103666398703</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1373871886174344</v>
+        <v>-0.142332037911442</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1187230022382589</v>
+        <v>-0.004238077471561271</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001696720539907596</v>
+        <v>0.001692050007405917</v>
       </c>
       <c r="G2" t="n">
-        <v>1.981667878716774</v>
+        <v>2.536557099760292</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4328157100735083</v>
+        <v>-0.2679240341459336</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
